--- a/utils/monday_sprint_sprint_2025-20.xlsx
+++ b/utils/monday_sprint_sprint_2025-20.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="330">
   <si>
     <t>Ticket</t>
   </si>
@@ -213,6 +213,9 @@
     <t>31/01/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -330,7 +333,7 @@
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>Junho</t>
@@ -507,7 +510,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -654,7 +657,7 @@
     <t>17/09/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>32353</t>
@@ -1992,21 +1995,21 @@
         <v>65</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -2018,10 +2021,10 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>30</v>
@@ -2039,7 +2042,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>26</v>
@@ -2050,22 +2053,22 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>30</v>
@@ -2094,22 +2097,22 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>30</v>
@@ -2138,7 +2141,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -2150,10 +2153,10 @@
         <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2194,10 +2197,10 @@
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>30</v>
@@ -2226,7 +2229,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2238,10 +2241,10 @@
         <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>30</v>
@@ -2270,7 +2273,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2282,10 +2285,10 @@
         <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2314,7 +2317,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2326,10 +2329,10 @@
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>30</v>
@@ -2350,7 +2353,7 @@
         <v>31</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>24</v>
@@ -2358,7 +2361,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2370,10 +2373,10 @@
         <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2402,22 +2405,22 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2458,7 +2461,7 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
@@ -2476,21 +2479,21 @@
         <v>65</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2502,7 +2505,7 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>24</v>
@@ -2517,7 +2520,7 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
@@ -2529,12 +2532,12 @@
         <v>32</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2546,10 +2549,10 @@
         <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2590,10 +2593,10 @@
         <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>30</v>
@@ -2634,10 +2637,10 @@
         <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>30</v>
@@ -2666,7 +2669,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2678,25 +2681,25 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>31</v>
@@ -2705,12 +2708,12 @@
         <v>32</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2722,10 +2725,10 @@
         <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>30</v>
@@ -2754,7 +2757,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2766,10 +2769,10 @@
         <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2798,7 +2801,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2810,10 +2813,10 @@
         <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>30</v>
@@ -2842,7 +2845,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2854,10 +2857,10 @@
         <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>30</v>
@@ -2898,10 +2901,10 @@
         <v>24</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>30</v>
@@ -2930,7 +2933,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2942,10 +2945,10 @@
         <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>30</v>
@@ -2974,7 +2977,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2986,10 +2989,10 @@
         <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -3018,7 +3021,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3030,10 +3033,10 @@
         <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>30</v>
@@ -3062,7 +3065,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -3074,10 +3077,10 @@
         <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -3106,7 +3109,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3118,10 +3121,10 @@
         <v>24</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>30</v>
@@ -3150,7 +3153,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3162,10 +3165,10 @@
         <v>24</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3194,7 +3197,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3206,10 +3209,10 @@
         <v>24</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3238,7 +3241,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3250,10 +3253,10 @@
         <v>24</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>30</v>
@@ -3274,7 +3277,7 @@
         <v>47</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>24</v>
@@ -3282,7 +3285,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3294,10 +3297,10 @@
         <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>30</v>
@@ -3326,7 +3329,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3338,10 +3341,10 @@
         <v>24</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3370,7 +3373,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3382,10 +3385,10 @@
         <v>24</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>30</v>
@@ -3406,7 +3409,7 @@
         <v>31</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>24</v>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3426,10 +3429,10 @@
         <v>24</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3470,7 +3473,7 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
@@ -3502,7 +3505,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3514,10 +3517,10 @@
         <v>24</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>30</v>
@@ -3546,7 +3549,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3558,10 +3561,10 @@
         <v>24</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>30</v>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3602,10 +3605,10 @@
         <v>24</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>30</v>
@@ -3634,7 +3637,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3646,25 +3649,25 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>31</v>
@@ -3673,12 +3676,12 @@
         <v>37</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3690,25 +3693,25 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>64</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>31</v>
@@ -3722,7 +3725,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3734,10 +3737,10 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>30</v>
@@ -3766,7 +3769,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3778,10 +3781,10 @@
         <v>24</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>30</v>
@@ -3810,7 +3813,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3822,25 +3825,25 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>31</v>
@@ -3849,12 +3852,12 @@
         <v>32</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3866,10 +3869,10 @@
         <v>24</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>30</v>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3910,10 +3913,10 @@
         <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>30</v>
@@ -3942,7 +3945,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3954,10 +3957,10 @@
         <v>24</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>30</v>
@@ -3986,7 +3989,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3998,10 +4001,10 @@
         <v>24</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -4030,7 +4033,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4042,10 +4045,10 @@
         <v>24</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4063,10 +4066,10 @@
         <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>24</v>
@@ -4074,7 +4077,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4086,10 +4089,10 @@
         <v>24</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>30</v>
@@ -4118,7 +4121,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4130,10 +4133,10 @@
         <v>24</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>30</v>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4174,10 +4177,10 @@
         <v>24</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>30</v>
@@ -4206,7 +4209,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4218,10 +4221,10 @@
         <v>24</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4250,7 +4253,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4262,22 +4265,22 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>24</v>
@@ -4286,15 +4289,15 @@
         <v>47</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4306,10 +4309,10 @@
         <v>24</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>30</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4350,10 +4353,10 @@
         <v>24</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>30</v>
@@ -4382,7 +4385,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4394,10 +4397,10 @@
         <v>24</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>30</v>
@@ -4426,66 +4429,66 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>30</v>
@@ -4514,7 +4517,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4526,10 +4529,10 @@
         <v>24</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>30</v>
@@ -4558,7 +4561,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4570,10 +4573,10 @@
         <v>24</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>30</v>
@@ -4602,7 +4605,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4614,10 +4617,10 @@
         <v>24</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4646,7 +4649,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4658,10 +4661,10 @@
         <v>24</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>30</v>
@@ -4690,7 +4693,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4702,25 +4705,25 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>31</v>
@@ -4729,12 +4732,12 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4746,22 +4749,22 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>24</v>
@@ -4773,12 +4776,12 @@
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4790,10 +4793,10 @@
         <v>24</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>30</v>
@@ -4811,7 +4814,7 @@
         <v>24</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>32</v>
@@ -4834,10 +4837,10 @@
         <v>24</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>30</v>
@@ -4866,22 +4869,22 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -4910,7 +4913,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4922,10 +4925,10 @@
         <v>24</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>30</v>
@@ -4954,22 +4957,22 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -4998,7 +5001,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5010,10 +5013,10 @@
         <v>24</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>30</v>
@@ -5042,22 +5045,22 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>30</v>
@@ -5086,7 +5089,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5098,10 +5101,10 @@
         <v>24</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>30</v>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5142,25 +5145,25 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>31</v>
@@ -5169,12 +5172,12 @@
         <v>37</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5186,25 +5189,25 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>31</v>
@@ -5213,12 +5216,12 @@
         <v>37</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5230,25 +5233,25 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>31</v>
@@ -5257,12 +5260,12 @@
         <v>37</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5274,7 +5277,7 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>24</v>
@@ -5289,7 +5292,7 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>24</v>
@@ -5301,7 +5304,7 @@
         <v>32</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -5318,10 +5321,10 @@
         <v>24</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>30</v>
@@ -5350,7 +5353,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5362,10 +5365,10 @@
         <v>24</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5394,7 +5397,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5406,10 +5409,10 @@
         <v>24</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5438,7 +5441,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5450,10 +5453,10 @@
         <v>24</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -5482,7 +5485,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5494,10 +5497,10 @@
         <v>24</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5538,10 +5541,10 @@
         <v>24</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
@@ -5570,7 +5573,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5582,10 +5585,10 @@
         <v>24</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5626,10 +5629,10 @@
         <v>24</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5670,10 +5673,10 @@
         <v>24</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -5702,7 +5705,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5714,10 +5717,10 @@
         <v>24</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
@@ -5746,7 +5749,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -5758,10 +5761,10 @@
         <v>24</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
@@ -5790,7 +5793,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -5802,10 +5805,10 @@
         <v>24</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>30</v>
@@ -5826,7 +5829,7 @@
         <v>47</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>24</v>
@@ -5834,7 +5837,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -5846,10 +5849,10 @@
         <v>17</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
@@ -5861,7 +5864,7 @@
         <v>22</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>24</v>
@@ -5870,15 +5873,15 @@
         <v>47</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -5890,10 +5893,10 @@
         <v>24</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>30</v>
@@ -5914,7 +5917,7 @@
         <v>31</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>24</v>
@@ -5922,7 +5925,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
@@ -5934,10 +5937,10 @@
         <v>24</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>30</v>
@@ -5958,7 +5961,7 @@
         <v>31</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>24</v>
@@ -5966,7 +5969,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -5978,10 +5981,10 @@
         <v>24</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>30</v>
@@ -6002,7 +6005,7 @@
         <v>31</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>24</v>
@@ -6010,7 +6013,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>15</v>
@@ -6022,10 +6025,10 @@
         <v>24</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>20</v>
@@ -6043,10 +6046,10 @@
         <v>24</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N105" s="2" t="s">
         <v>24</v>
@@ -6054,7 +6057,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
@@ -6066,10 +6069,10 @@
         <v>24</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>30</v>
@@ -6090,7 +6093,7 @@
         <v>31</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N106" s="2" t="s">
         <v>24</v>
@@ -6098,22 +6101,22 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>30</v>
@@ -6134,7 +6137,7 @@
         <v>31</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>24</v>
@@ -6142,7 +6145,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -6154,10 +6157,10 @@
         <v>24</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>30</v>
@@ -6178,7 +6181,7 @@
         <v>57</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N108" s="2" t="s">
         <v>24</v>
@@ -6186,7 +6189,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -6198,10 +6201,10 @@
         <v>24</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>30</v>
@@ -6222,7 +6225,7 @@
         <v>47</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N109" s="2" t="s">
         <v>24</v>
@@ -6230,7 +6233,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>15</v>
@@ -6242,10 +6245,10 @@
         <v>24</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>20</v>
@@ -6266,7 +6269,7 @@
         <v>31</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N110" s="2" t="s">
         <v>24</v>
@@ -6274,7 +6277,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>15</v>
@@ -6286,25 +6289,25 @@
         <v>17</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>31</v>
@@ -6313,12 +6316,12 @@
         <v>37</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
@@ -6330,10 +6333,10 @@
         <v>24</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>30</v>
@@ -6354,7 +6357,7 @@
         <v>47</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>24</v>
@@ -6374,10 +6377,10 @@
         <v>24</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>30</v>
@@ -6398,7 +6401,7 @@
         <v>31</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>24</v>
@@ -6406,7 +6409,7 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>15</v>
@@ -6418,10 +6421,10 @@
         <v>24</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>30</v>
@@ -6439,10 +6442,10 @@
         <v>24</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>24</v>
@@ -6450,7 +6453,7 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>15</v>
@@ -6462,10 +6465,10 @@
         <v>24</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>30</v>
@@ -6486,7 +6489,7 @@
         <v>31</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>24</v>
@@ -6494,7 +6497,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>15</v>
@@ -6506,10 +6509,10 @@
         <v>24</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>20</v>
@@ -6530,7 +6533,7 @@
         <v>31</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>24</v>
@@ -6538,7 +6541,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>15</v>
@@ -6550,10 +6553,10 @@
         <v>24</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>20</v>
@@ -6574,7 +6577,7 @@
         <v>31</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>24</v>
@@ -6582,7 +6585,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>15</v>
@@ -6594,10 +6597,10 @@
         <v>24</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>20</v>
@@ -6618,7 +6621,7 @@
         <v>31</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>24</v>
@@ -6626,7 +6629,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>15</v>
@@ -6638,39 +6641,39 @@
         <v>17</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>31</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>15</v>
@@ -6682,10 +6685,10 @@
         <v>24</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>20</v>
@@ -6706,7 +6709,7 @@
         <v>31</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>24</v>
@@ -6714,7 +6717,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -6726,10 +6729,10 @@
         <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>20</v>
@@ -6750,7 +6753,7 @@
         <v>57</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N121" s="2" t="s">
         <v>24</v>
@@ -6758,7 +6761,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>15</v>
@@ -6770,10 +6773,10 @@
         <v>24</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>30</v>
@@ -6794,7 +6797,7 @@
         <v>47</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>24</v>
@@ -6814,10 +6817,10 @@
         <v>24</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>30</v>
@@ -6838,7 +6841,7 @@
         <v>47</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>24</v>
@@ -6846,7 +6849,7 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>15</v>
@@ -6858,10 +6861,10 @@
         <v>24</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>20</v>
@@ -6882,7 +6885,7 @@
         <v>47</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>24</v>
@@ -6890,7 +6893,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>15</v>
@@ -6902,10 +6905,10 @@
         <v>24</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>30</v>
@@ -6926,7 +6929,7 @@
         <v>47</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>24</v>
@@ -6934,7 +6937,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>15</v>
@@ -6946,10 +6949,10 @@
         <v>24</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>30</v>
@@ -6970,7 +6973,7 @@
         <v>57</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N126" s="2" t="s">
         <v>24</v>
@@ -6978,7 +6981,7 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>15</v>
@@ -6990,10 +6993,10 @@
         <v>24</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>20</v>
@@ -7014,7 +7017,7 @@
         <v>31</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N127" s="2" t="s">
         <v>24</v>
@@ -7022,7 +7025,7 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>15</v>
@@ -7034,10 +7037,10 @@
         <v>24</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>20</v>
@@ -7058,7 +7061,7 @@
         <v>31</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N128" s="2" t="s">
         <v>24</v>
@@ -7066,7 +7069,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>15</v>
@@ -7078,10 +7081,10 @@
         <v>24</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>30</v>
@@ -7102,7 +7105,7 @@
         <v>47</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>24</v>
@@ -7121,23 +7124,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7145,16 +7148,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7173,7 +7176,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -7186,7 +7189,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -7194,7 +7197,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -7225,12 +7228,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B2">
         <v>128</v>
@@ -7254,25 +7257,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7289,13 +7292,13 @@
         <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7307,10 +7310,10 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -7327,7 +7330,7 @@
         <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K11">
         <v>128</v>
@@ -7342,12 +7345,12 @@
         <v>37</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -7359,7 +7362,7 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -7368,18 +7371,18 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -7394,7 +7397,7 @@
         <v>32</v>
       </c>
       <c r="Q13">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
@@ -7405,22 +7408,22 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q14">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -7433,7 +7436,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -7449,7 +7452,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -7460,7 +7463,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7468,16 +7471,16 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7488,10 +7491,10 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7505,105 +7508,105 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-20.xlsx
+++ b/utils/monday_sprint_sprint_2025-20.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="365">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -63,270 +63,309 @@
     <t>33549</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Integração de sistema Logística x data book - Automação Planilha</t>
+  </si>
+  <si>
+    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Rosivaldo Silva</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>Em Análise</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>18013073955</t>
+  </si>
+  <si>
     <t>Setor não informado</t>
   </si>
   <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Integração de sistema Logística x data book - Automação Planilha</t>
-  </si>
-  <si>
-    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Rosivaldo Silva</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>22/08/2025</t>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Incluir informação - Sequencia</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>22/09/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>18012999616</t>
+  </si>
+  <si>
+    <t>Sistema de Panelas - Reunião</t>
+  </si>
+  <si>
+    <t>10006682913</t>
+  </si>
+  <si>
+    <t>Manter a integridade de valores quando houver tabela intermediária e posterior registro na tabela final.</t>
+  </si>
+  <si>
+    <t>09/09/2025</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>18013257107</t>
+  </si>
+  <si>
+    <t>Gráfico refugo diário - SENSE</t>
+  </si>
+  <si>
+    <t>24/09/2025</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>18005107006</t>
+  </si>
+  <si>
+    <t>Sequencia de Pre Produtivo</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>18003636494</t>
+  </si>
+  <si>
+    <t>Relatórios de requisições</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>18003959422</t>
+  </si>
+  <si>
+    <t>Chamado para Inclusão da TE - 290 no sistema de MPO</t>
+  </si>
+  <si>
+    <t>18013279391</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Criar documento na ordem de coleta (Puxar NF e invoice)</t>
+  </si>
+  <si>
+    <t>18012849238</t>
+  </si>
+  <si>
+    <t>Desenvolver Aplicação Qlik Sense Dados Custeio - Chamado Principal</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>18013279465</t>
+  </si>
+  <si>
+    <t>Reorganizar filtro x campos na tela de visão master</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira (apresentação)</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>18005118957</t>
+  </si>
+  <si>
+    <t>Processo ALTO IMPACTO</t>
+  </si>
+  <si>
+    <t>01/10/2025</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>18013256816</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>FTF Qualidade</t>
+  </si>
+  <si>
+    <t>18003442447</t>
+  </si>
+  <si>
+    <t>Aplicação Resumo Carteira</t>
+  </si>
+  <si>
+    <t>9879709110</t>
+  </si>
+  <si>
+    <t>Indicador Cobertura de Estoques</t>
+  </si>
+  <si>
+    <t>10006670009</t>
+  </si>
+  <si>
+    <t>Bloquear apontamentos cuja data do apontamento é anterior ao período finalizado</t>
+  </si>
+  <si>
+    <t>18003942755</t>
+  </si>
+  <si>
+    <t>Apontamento jato grande</t>
+  </si>
+  <si>
+    <t>9879801990</t>
+  </si>
+  <si>
+    <t>Divergência de peso no deposito após fechamento de indicadores</t>
+  </si>
+  <si>
+    <t>9985270020</t>
+  </si>
+  <si>
+    <t>Manutenção Dalca e Lianco</t>
+  </si>
+  <si>
+    <t>05/09/2025</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>18013142484</t>
+  </si>
+  <si>
+    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
+  </si>
+  <si>
+    <t>28/09/2025</t>
+  </si>
+  <si>
+    <t>18012849485</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de aplicação de custos por refugo</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Integração CRM - Tarefa para disparar integrações</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Em Análise</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>33713</t>
-  </si>
-  <si>
-    <t>Categoria não informada</t>
-  </si>
-  <si>
-    <t>Incluir informação - Sequencia</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Solicitante não informado</t>
-  </si>
-  <si>
-    <t>Equipe não informada</t>
-  </si>
-  <si>
-    <t>22/09/2025</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>33077</t>
-  </si>
-  <si>
-    <t>Sistema de Panelas - Reunião</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Manter a integridade de valores quando houver tabela intermediária e posterior registro na tabela final.</t>
-  </si>
-  <si>
-    <t>09/09/2025</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>33401</t>
-  </si>
-  <si>
-    <t>Gráfico refugo diário - SENSE</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>33651</t>
-  </si>
-  <si>
-    <t>Sequencia de Pre Produtivo</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>34132</t>
-  </si>
-  <si>
-    <t>Relatórios de requisições</t>
-  </si>
-  <si>
-    <t>34121</t>
-  </si>
-  <si>
-    <t>Chamado para Inclusão da TE - 290 no sistema de MPO</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Criar documento na ordem de coleta (Puxar NF e invoice)</t>
-  </si>
-  <si>
-    <t>24641</t>
-  </si>
-  <si>
-    <t>Desenvolver Aplicação Qlik Sense Dados Custeio - Chamado Principal</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>Reorganizar filtro x campos na tela de visão master</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira (apresentação)</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>33439</t>
-  </si>
-  <si>
-    <t>Processo ALTO IMPACTO</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>33288</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>FTF Qualidade</t>
-  </si>
-  <si>
-    <t>34134</t>
-  </si>
-  <si>
-    <t>Aplicação Resumo Carteira</t>
-  </si>
-  <si>
-    <t>33588</t>
-  </si>
-  <si>
-    <t>Indicador Cobertura de Estoques</t>
-  </si>
-  <si>
-    <t>Bloquear apontamentos cuja data do apontamento é anterior ao período finalizado</t>
-  </si>
-  <si>
-    <t>34123</t>
-  </si>
-  <si>
-    <t>Apontamento jato grande</t>
-  </si>
-  <si>
-    <t>33537</t>
-  </si>
-  <si>
-    <t>Divergência de peso no deposito após fechamento de indicadores</t>
-  </si>
-  <si>
-    <t>33840</t>
-  </si>
-  <si>
-    <t>Manutenção Dalca e Lianco</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>32723</t>
-  </si>
-  <si>
-    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
-  </si>
-  <si>
-    <t>33023</t>
-  </si>
-  <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>Desenvolvimento de aplicação de custos por refugo</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Integração CRM - Tarefa para disparar integrações</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
-    <t>34073</t>
+    <t>18004114785</t>
   </si>
   <si>
     <t>HUB de aplicações</t>
   </si>
   <si>
+    <t>05/10/2025</t>
+  </si>
+  <si>
+    <t>10006687801</t>
+  </si>
+  <si>
     <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
   </si>
   <si>
+    <t>29/09/2025</t>
+  </si>
+  <si>
+    <t>10007170990</t>
+  </si>
+  <si>
     <t>Teste com Trigger - Checagem do fechamento do custo</t>
   </si>
   <si>
@@ -348,112 +387,124 @@
     <t>17/03/2026</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>18013142936</t>
   </si>
   <si>
     <t>Conversão KB TOTO - Relatórios</t>
   </si>
   <si>
-    <t>33772</t>
+    <t>18013073822</t>
   </si>
   <si>
     <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
   </si>
   <si>
-    <t>34031</t>
+    <t>18004156264</t>
   </si>
   <si>
     <t>Melhoria Tela Tratamento térmico</t>
   </si>
   <si>
-    <t>33914</t>
+    <t>18013000246</t>
   </si>
   <si>
     <t>Centro de custo</t>
   </si>
   <si>
+    <t>18012849704</t>
+  </si>
+  <si>
     <t>Validar apontamentos com longos períodos.</t>
   </si>
   <si>
-    <t>33618</t>
+    <t>18012849395</t>
   </si>
   <si>
     <t>Bloco K - Ajuste no filtro de seleção das sequências oriundas do cálculo do custo.</t>
   </si>
   <si>
-    <t>34108</t>
+    <t>18013618172</t>
+  </si>
+  <si>
+    <t>18004076007</t>
   </si>
   <si>
     <t>Incluir coluna - Planilhão USE</t>
   </si>
   <si>
-    <t>33807</t>
+    <t>18013339337</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO UPR MESA REDONDA</t>
   </si>
   <si>
-    <t>33662</t>
+    <t>18013142696</t>
   </si>
   <si>
     <t>Controle de documentação de exportação</t>
   </si>
   <si>
-    <t>33855</t>
+    <t>18013000332</t>
   </si>
   <si>
     <t>PMOV</t>
   </si>
   <si>
-    <t>33009</t>
+    <t>18013339862</t>
   </si>
   <si>
     <t>Controle de indicadores ao vivo</t>
   </si>
   <si>
-    <t>33660</t>
+    <t>9985815201</t>
   </si>
   <si>
     <t>Apontamento por botoeiras na Carrossel</t>
   </si>
   <si>
-    <t>33657</t>
+    <t>18013071165</t>
   </si>
   <si>
     <t>ABERTURA DE SALDO SETOR 597 X MOVIMENTAÇÃO SETOR 7299</t>
   </si>
   <si>
-    <t>32588</t>
+    <t>02/10/2025</t>
+  </si>
+  <si>
+    <t>18000532587</t>
   </si>
   <si>
     <t>Baixa de Estoque de Embalagem Expedição - Gerar requisição</t>
   </si>
   <si>
-    <t>33632</t>
+    <t>9985827897</t>
   </si>
   <si>
     <t>Cálculo de carga - Sistema de corridas - Reunião</t>
   </si>
   <si>
+    <t>18013071197</t>
+  </si>
+  <si>
     <t>Interface para o usuário realizar a integração com OpCenter</t>
   </si>
   <si>
     <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
   </si>
   <si>
-    <t>32536</t>
+    <t>18013074280</t>
   </si>
   <si>
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
   </si>
   <si>
-    <t>34208</t>
+    <t>18003027404</t>
   </si>
   <si>
     <t>Alterar gráfico na aplicação IROG - Usinagem</t>
   </si>
   <si>
-    <t>31685</t>
+    <t>18013072008</t>
   </si>
   <si>
     <t>Planilhão via Qlik sense</t>
@@ -462,6 +513,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Saneamento de dados para APS</t>
   </si>
   <si>
@@ -483,45 +537,51 @@
     <t>Marcelo Americo</t>
   </si>
   <si>
-    <t>32677</t>
+    <t>18012849967</t>
   </si>
   <si>
     <t>PDI - Fixar colunas de identificação das cotas</t>
   </si>
   <si>
-    <t>34200</t>
+    <t>18003048515</t>
   </si>
   <si>
     <t>INCLUSÃO DE TIPOS DIFERENTES DE OTFs</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>18012849879</t>
   </si>
   <si>
     <t>Consulta de divergências - Registro Pintura</t>
   </si>
   <si>
-    <t>33998</t>
+    <t>18004420792</t>
   </si>
   <si>
     <t>Lead time</t>
   </si>
   <si>
-    <t>31270</t>
+    <t>18013072408</t>
   </si>
   <si>
     <t>MELHORIAS FLUXO 109 REVISÕES</t>
   </si>
   <si>
+    <t>18012850266</t>
+  </si>
+  <si>
     <t>PDI - Inspeção - Cotas informadas.</t>
   </si>
   <si>
-    <t>34029</t>
+    <t>18004185999</t>
   </si>
   <si>
     <t>Nota técnica 2025.002 - Alteração no XML da nota</t>
   </si>
   <si>
+    <t>18132302235</t>
+  </si>
+  <si>
     <t>Nota técnica 2025.002 - Alteração no XML da nota - Homologação</t>
   </si>
   <si>
@@ -534,22 +594,25 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>33992</t>
+    <t>18004438019</t>
   </si>
   <si>
     <t>ACVO - SISTEMA SEQUÊNCIA EM ABERTO POR SETOR</t>
   </si>
   <si>
-    <t>34198</t>
+    <t>18015665261</t>
   </si>
   <si>
     <t>Sistema Importação - Flag importador</t>
   </si>
   <si>
+    <t>18003069207</t>
+  </si>
+  <si>
     <t>Sistema Importação</t>
   </si>
   <si>
-    <t>25418</t>
+    <t>18013072252</t>
   </si>
   <si>
     <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
@@ -558,9 +621,6 @@
     <t>33965</t>
   </si>
   <si>
-    <t>Fundição</t>
-  </si>
-  <si>
     <t>Apontamento de moldes Carrossel</t>
   </si>
   <si>
@@ -570,19 +630,19 @@
     <t>Matheus Rodrigues de Almeida</t>
   </si>
   <si>
-    <t>33967</t>
+    <t>18004473274</t>
   </si>
   <si>
     <t>Criar um usuário mestre</t>
   </si>
   <si>
-    <t>33594</t>
+    <t>18013071820</t>
   </si>
   <si>
     <t>ESTORNO DE MOVIMENTAÇÃO EM VÁRIAS SEQUÊNCIAS</t>
   </si>
   <si>
-    <t>34152</t>
+    <t>18003324101</t>
   </si>
   <si>
     <t>Relatório WMS - Consulta O.M</t>
@@ -600,91 +660,97 @@
     <t>Jacson Schneider Movidesk</t>
   </si>
   <si>
-    <t>34164</t>
+    <t>18003099932</t>
   </si>
   <si>
     <t>Relatório WMS - Consulta movimentação</t>
   </si>
   <si>
-    <t>34154</t>
+    <t>18003134535</t>
   </si>
   <si>
     <t>MODELO NÃO DEFINIDO FTF X ANÁLISE CRÍTICA</t>
   </si>
   <si>
-    <t>33978</t>
+    <t>18004589879</t>
   </si>
   <si>
     <t>Altona || Atalho para cadastro de materiais no sistema da contabilidade</t>
   </si>
   <si>
+    <t>18012850394</t>
+  </si>
+  <si>
     <t>Relação de aplicações WEB</t>
   </si>
   <si>
-    <t>33878</t>
+    <t>18013256248</t>
   </si>
   <si>
     <t>Gráfico de Kg de eletrodo por tonelada de peça produzida</t>
   </si>
   <si>
-    <t>34157</t>
+    <t>18003113902</t>
   </si>
   <si>
     <t>Aplicação de Solda</t>
   </si>
   <si>
-    <t>32353</t>
+    <t>27/09/2025</t>
+  </si>
+  <si>
+    <t>18012850038</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>33441</t>
+    <t>18013072543</t>
   </si>
   <si>
     <t>Melhoria de copia de analise e processos</t>
   </si>
   <si>
+    <t>18013072686</t>
+  </si>
+  <si>
     <t>Verificar apontamentos com origem na solda - Não permitir Alterar</t>
   </si>
   <si>
-    <t>34138</t>
+    <t>18003346812</t>
   </si>
   <si>
     <t>Datas sistema mapeamento digital</t>
   </si>
   <si>
-    <t>33867</t>
+    <t>18012871859</t>
   </si>
   <si>
     <t>Arvore de ativos na WEB</t>
   </si>
   <si>
-    <t>32404</t>
+    <t>18013256039</t>
   </si>
   <si>
     <t>BI para análises das auditorias de CIPA</t>
   </si>
   <si>
-    <t>32974</t>
+    <t>18012871438</t>
   </si>
   <si>
     <t>Projeto BI IROG SPA - Criar tela de cadastro de metas para BI</t>
   </si>
   <si>
-    <t>33966</t>
+    <t>30/09/2025</t>
+  </si>
+  <si>
+    <t>18004655927</t>
   </si>
   <si>
     <t>Issues with Proformas</t>
   </si>
   <si>
-    <t>33519</t>
+    <t>18012871798</t>
   </si>
   <si>
     <t>Backlog de alterações - Sistema Manutenção -&gt; SS e OS</t>
@@ -693,9 +759,6 @@
     <t>Realizar procedimento para deletar os dados do APS</t>
   </si>
   <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
     <t>Preparar o procedimento para leitura do plano ativo</t>
   </si>
   <si>
@@ -705,60 +768,81 @@
     <t>Integração CRM - Carga Ofertas</t>
   </si>
   <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>18032155757</t>
+  </si>
+  <si>
     <t>Cálculo de Horas para o BI por Macro área - Criar sub nível na tabela [CustoMes] para salvar o tempo por sequência</t>
   </si>
   <si>
-    <t>24/09/2025</t>
-  </si>
-  <si>
-    <t>30796</t>
+    <t>18037057568</t>
   </si>
   <si>
     <t>Mudar a visão para tabs: 1- cabeçalho / 2- ações / 3- evidências</t>
   </si>
   <si>
+    <t>18037094365</t>
+  </si>
+  <si>
     <t>Habilitar opção para GIQ poder cadastrar setor (Usinagem / Fundição / Inspeção / Acabamento) e também área (Usinagem / Ajustagem / Pintura / Rebarbação 3 ...);</t>
   </si>
   <si>
+    <t>18037113420</t>
+  </si>
+  <si>
     <t>Na tela home, transformar a visão em tabs. Criar possibilidade de finalizar a ação e também cadastrar evidência;</t>
   </si>
   <si>
+    <t>18037129280</t>
+  </si>
+  <si>
     <t>Alterar a lista de Status</t>
   </si>
   <si>
-    <t>31347</t>
+    <t>18041714673</t>
   </si>
   <si>
     <t>Criar na tela WCPP22K quatro flags que permitam ser selecionadas a qualquer momento para pesquisa de CPPs que possuam os seguintes controles sequenciais:</t>
   </si>
   <si>
-    <t>25/09/2025</t>
+    <t>18041741160</t>
   </si>
   <si>
     <t>No sistema de Ensaios Destrutivos [tela UCQ281K] deve possuir um novo campo logo ao lado do campo “Sequência de Fundição” para que o usuário informe se é um ensaio de peça ou de bloco:</t>
   </si>
   <si>
+    <t>18041743838</t>
+  </si>
+  <si>
     <t>Nas consultas, além de trazer os valores do ensaio deve também trazer a sequência (bloco e/ou peça) a qual resultou nesses valores</t>
   </si>
   <si>
+    <t>18041765556</t>
+  </si>
+  <si>
     <t>A peça que for selecionada pelo sistema para ser destruída deve ser destacada em cor ROSA em todas as telas de consulta e movimentação do sistema PCP [são os atalhos Alts+A, M, K, I, D e H].</t>
   </si>
   <si>
+    <t>18041770717</t>
+  </si>
+  <si>
     <t>Criar novo setor (PENDÊNCIA ENSAIOS MECÂNICOS DE PEÇA) – 5XXX. Este setor deve ser aberto logo após o setor 7209 para as peças da corrida de aciaria que possuir uma peça definida para ensaios mecânicos:</t>
   </si>
   <si>
+    <t>18041775907</t>
+  </si>
+  <si>
     <t>Criar uma nova regra no sistema para que também tenha um controle por tempo em dias (permitir até três dígitos) na tela [TANCR018] conforme imagem abaixo e que também seja consultada e/ou revisada na tela [WCPP45ED]:</t>
   </si>
   <si>
-    <t>33942</t>
+    <t>18078013974</t>
   </si>
   <si>
     <t>HISTÓRICO DE REVISÃO CHECKLIST DO AP119</t>
   </si>
   <si>
-    <t>30/09/2025</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -774,19 +858,22 @@
     <t>02/06/2026</t>
   </si>
   <si>
-    <t>33688</t>
+    <t>18078015135</t>
   </si>
   <si>
     <t>Remover do sistema etapa da coquilha</t>
   </si>
   <si>
-    <t>34166</t>
+    <t>18078015290</t>
   </si>
   <si>
     <t>ALTERAÇÃO NA CÓPIA DE FTF'S</t>
   </si>
   <si>
-    <t>33794</t>
+    <t>18078015362</t>
+  </si>
+  <si>
+    <t>18078016096</t>
   </si>
   <si>
     <t>Melhoria B.I - Análise</t>
@@ -795,31 +882,31 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>29476</t>
+    <t>18078016254</t>
   </si>
   <si>
     <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
   </si>
   <si>
-    <t>33599</t>
+    <t>18078016720</t>
   </si>
   <si>
     <t>Aplicação Insertos Usinagem</t>
   </si>
   <si>
-    <t>29123</t>
+    <t>18078016899</t>
   </si>
   <si>
     <t>B.I ordens de manutenção maquinas pneumáticas</t>
   </si>
   <si>
-    <t>32287</t>
+    <t>18078017133</t>
   </si>
   <si>
     <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião</t>
   </si>
   <si>
-    <t>33963</t>
+    <t>18078017396</t>
   </si>
   <si>
     <t>Publicar aplicações de apontamento (POSTMOVTO)</t>
@@ -828,39 +915,54 @@
     <t>Extração de dados IROG Usinagem</t>
   </si>
   <si>
-    <t>33331</t>
+    <t>18078018265</t>
   </si>
   <si>
     <t>[APS] - Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
   </si>
   <si>
+    <t>18078019651</t>
+  </si>
+  <si>
     <t>Evoluir como o período finalizado.</t>
   </si>
   <si>
-    <t>33933</t>
+    <t>18078019971</t>
   </si>
   <si>
     <t>Criar campo para gatilho de analise de causa raiz</t>
   </si>
   <si>
-    <t>33834</t>
+    <t>18078020091</t>
   </si>
   <si>
     <t>Inclusão de custo de máquina parada na origem de custo dos custos de manutenção</t>
   </si>
   <si>
+    <t>18078021518</t>
+  </si>
+  <si>
     <t>Tab evidência, deverá aparecer uma lista das ações criadas, para anexar a evidência correspondente. O responsável pelo plano pode anexar em qualquer ação; os demais podem anexar apenas em ação de sua responsabilidade;</t>
   </si>
   <si>
+    <t>18078021616</t>
+  </si>
+  <si>
     <t>Usuário responsável pela sua ação terá permissão para alterar todos os campos da sua ação;</t>
   </si>
   <si>
+    <t>18078021713</t>
+  </si>
+  <si>
     <t>Usuário cadastrando um novo plano, deve ser considerado o responsável por esse plano em questão. A GIQ deverá poder alterar o responsável caso necessário;</t>
   </si>
   <si>
     <t>33956</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Definição de metas de custos de manutenção</t>
   </si>
   <si>
@@ -870,55 +972,67 @@
     <t>Robmar Xavier</t>
   </si>
   <si>
+    <t>18078021828</t>
+  </si>
+  <si>
     <t>Criar uma lista suspensa para selecionar os nomes dos participantes do “Grupo de Trabalho”. Atualmente está texto, mudar esse padrão;</t>
   </si>
   <si>
+    <t>18078021984</t>
+  </si>
+  <si>
     <t>Criar um ícone para impressão do plano;</t>
   </si>
   <si>
-    <t>33955</t>
+    <t>18078020375</t>
   </si>
   <si>
     <t>CADASTROS CPP - ACABAMENTO</t>
   </si>
   <si>
+    <t>18078019766</t>
+  </si>
+  <si>
     <t>Cálculo de Horas para o BI por Macro área - Revisar a fórmula do cálculo de em todas as macro áreas</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>18078020705</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>32685</t>
+    <t>18078023507</t>
   </si>
   <si>
     <t>Qlik - Vinculo de Atualização Comparação de volume</t>
   </si>
   <si>
-    <t>33695</t>
+    <t>18078029475</t>
   </si>
   <si>
     <t>Selecionador de Componente e modo de falha</t>
   </si>
   <si>
+    <t>18078033818</t>
+  </si>
+  <si>
     <t>Na tela home criar possibilidade de clicar no número do plano e abrir o plano de ação completo</t>
   </si>
   <si>
-    <t>27502</t>
+    <t>18078516984</t>
   </si>
   <si>
     <t>Cartão vazamento projeto melhoria</t>
   </si>
   <si>
-    <t>29536</t>
+    <t>18095509282</t>
   </si>
   <si>
     <t>Ajuste do sistema de impressão de formulários (copy)</t>
   </si>
   <si>
-    <t>02/10/2025</t>
+    <t>25/08/2025</t>
   </si>
   <si>
     <t>Dashboard de Change Log - Governança de TI</t>
@@ -927,7 +1041,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-20</t>
+    <t>Ago/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1527,40 +1641,40 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>28</v>
@@ -1574,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>41</v>
@@ -1589,25 +1703,25 @@
         <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>28</v>
@@ -1621,13 +1735,13 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>43</v>
@@ -1636,28 +1750,28 @@
         <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>39</v>
@@ -1665,40 +1779,40 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>27</v>
@@ -1712,46 +1826,46 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>39</v>
@@ -1759,46 +1873,46 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>39</v>
@@ -1806,46 +1920,46 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>39</v>
@@ -1853,43 +1967,43 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>28</v>
@@ -1900,40 +2014,40 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>27</v>
@@ -1947,43 +2061,43 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>28</v>
@@ -1994,43 +2108,43 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>28</v>
@@ -2041,46 +2155,46 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>39</v>
@@ -2088,43 +2202,43 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>28</v>
@@ -2135,46 +2249,46 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>39</v>
@@ -2182,40 +2296,40 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>27</v>
@@ -2229,46 +2343,46 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>39</v>
@@ -2276,46 +2390,46 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>39</v>
@@ -2323,43 +2437,43 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>28</v>
@@ -2370,46 +2484,46 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>39</v>
@@ -2417,40 +2531,40 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>27</v>
@@ -2464,40 +2578,40 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>27</v>
@@ -2511,46 +2625,46 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>39</v>
@@ -2558,40 +2672,40 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>27</v>
@@ -2605,46 +2719,46 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>39</v>
@@ -2652,46 +2766,46 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>39</v>
@@ -2699,46 +2813,46 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>39</v>
@@ -2746,10 +2860,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -2758,31 +2872,31 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>28</v>
@@ -2793,43 +2907,43 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>28</v>
@@ -2840,40 +2954,40 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>27</v>
@@ -2887,46 +3001,46 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>39</v>
@@ -2934,43 +3048,43 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>28</v>
@@ -2981,43 +3095,43 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>28</v>
@@ -3028,43 +3142,43 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>28</v>
@@ -3075,40 +3189,40 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>27</v>
@@ -3122,46 +3236,46 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>39</v>
@@ -3169,43 +3283,43 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>28</v>
@@ -3216,43 +3330,43 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>28</v>
@@ -3263,43 +3377,43 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>28</v>
@@ -3310,43 +3424,43 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>28</v>
@@ -3357,46 +3471,46 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>39</v>
@@ -3404,43 +3518,43 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>28</v>
@@ -3451,46 +3565,46 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>39</v>
@@ -3498,46 +3612,46 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>39</v>
@@ -3545,40 +3659,40 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>27</v>
@@ -3604,7 +3718,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>20</v>
@@ -3619,7 +3733,7 @@
         <v>23</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>25</v>
@@ -3639,40 +3753,40 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>27</v>
@@ -3686,46 +3800,46 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>39</v>
@@ -3733,43 +3847,43 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>28</v>
@@ -3780,43 +3894,43 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>28</v>
@@ -3827,7 +3941,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3839,34 +3953,34 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>39</v>
@@ -3874,40 +3988,40 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>27</v>
@@ -3921,46 +4035,46 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>39</v>
@@ -3968,43 +4082,43 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>28</v>
@@ -4015,46 +4129,46 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>39</v>
@@ -4062,40 +4176,40 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>27</v>
@@ -4109,40 +4223,40 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>27</v>
@@ -4156,46 +4270,46 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>39</v>
@@ -4203,93 +4317,93 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>39</v>
@@ -4297,43 +4411,43 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>28</v>
@@ -4344,46 +4458,46 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>39</v>
@@ -4391,40 +4505,40 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>27</v>
@@ -4438,10 +4552,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>17</v>
@@ -4450,34 +4564,34 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>39</v>
@@ -4485,46 +4599,46 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>39</v>
@@ -4532,43 +4646,43 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>28</v>
@@ -4579,46 +4693,46 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>39</v>
@@ -4626,37 +4740,37 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>26</v>
@@ -4673,46 +4787,46 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>39</v>
@@ -4720,46 +4834,46 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>39</v>
@@ -4767,46 +4881,46 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>39</v>
@@ -4814,43 +4928,43 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>101</v>
+        <v>221</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>28</v>
@@ -4861,43 +4975,43 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>28</v>
@@ -4908,46 +5022,46 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>39</v>
@@ -4955,40 +5069,40 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>27</v>
@@ -5002,40 +5116,40 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>27</v>
@@ -5049,43 +5163,43 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>28</v>
@@ -5096,46 +5210,46 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>39</v>
@@ -5143,43 +5257,43 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>28</v>
@@ -5190,43 +5304,43 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>28</v>
@@ -5237,43 +5351,43 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>28</v>
@@ -5284,46 +5398,46 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>39</v>
@@ -5331,43 +5445,43 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>28</v>
@@ -5378,10 +5492,10 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>17</v>
@@ -5390,31 +5504,31 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>28</v>
@@ -5425,10 +5539,10 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>17</v>
@@ -5437,31 +5551,31 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>28</v>
@@ -5472,10 +5586,10 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
@@ -5484,31 +5598,31 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>28</v>
@@ -5519,43 +5633,43 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>28</v>
@@ -5566,43 +5680,43 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>28</v>
@@ -5613,43 +5727,43 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>28</v>
@@ -5660,43 +5774,43 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>28</v>
@@ -5707,40 +5821,40 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>27</v>
@@ -5754,43 +5868,43 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>28</v>
@@ -5801,43 +5915,43 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>28</v>
@@ -5848,43 +5962,43 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>28</v>
@@ -5895,43 +6009,43 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>28</v>
@@ -5942,43 +6056,43 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>28</v>
@@ -5989,43 +6103,43 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>28</v>
@@ -6036,43 +6150,43 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>28</v>
@@ -6083,46 +6197,46 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>39</v>
@@ -6130,10 +6244,10 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>17</v>
@@ -6142,34 +6256,34 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M101" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O101" s="2" t="s">
         <v>39</v>
@@ -6177,46 +6291,46 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O102" s="2" t="s">
         <v>39</v>
@@ -6224,46 +6338,46 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O103" s="2" t="s">
         <v>39</v>
@@ -6271,46 +6385,46 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>162</v>
+        <v>285</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O104" s="2" t="s">
         <v>39</v>
@@ -6318,46 +6432,46 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O105" s="2" t="s">
         <v>39</v>
@@ -6365,46 +6479,46 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>39</v>
@@ -6412,46 +6526,46 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O107" s="2" t="s">
         <v>39</v>
@@ -6459,46 +6573,46 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O108" s="2" t="s">
         <v>39</v>
@@ -6506,46 +6620,46 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M109" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O109" s="2" t="s">
         <v>39</v>
@@ -6553,46 +6667,46 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O110" s="2" t="s">
         <v>39</v>
@@ -6600,10 +6714,10 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>17</v>
@@ -6612,34 +6726,34 @@
         <v>18</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O111" s="2" t="s">
         <v>39</v>
@@ -6647,46 +6761,46 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M112" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O112" s="2" t="s">
         <v>39</v>
@@ -6694,46 +6808,46 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O113" s="2" t="s">
         <v>39</v>
@@ -6741,46 +6855,46 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M114" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O114" s="2" t="s">
         <v>39</v>
@@ -6788,46 +6902,46 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N115" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L115" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N115" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="O115" s="2" t="s">
         <v>39</v>
@@ -6835,46 +6949,46 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O116" s="2" t="s">
         <v>39</v>
@@ -6882,46 +6996,46 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O117" s="2" t="s">
         <v>39</v>
@@ -6929,46 +7043,46 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>232</v>
+        <v>312</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>39</v>
@@ -6976,10 +7090,10 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>16</v>
+        <v>315</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>17</v>
@@ -6988,34 +7102,34 @@
         <v>18</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O119" s="2" t="s">
         <v>39</v>
@@ -7023,46 +7137,46 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>39</v>
@@ -7070,46 +7184,46 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>232</v>
+        <v>321</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M121" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O121" s="2" t="s">
         <v>39</v>
@@ -7117,46 +7231,46 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M122" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O122" s="2" t="s">
         <v>39</v>
@@ -7164,46 +7278,46 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M123" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O123" s="2" t="s">
         <v>39</v>
@@ -7211,46 +7325,46 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M124" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>39</v>
@@ -7258,46 +7372,46 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M125" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>39</v>
@@ -7305,46 +7419,46 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M126" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>39</v>
@@ -7352,46 +7466,46 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O127" s="2" t="s">
         <v>39</v>
@@ -7399,46 +7513,46 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="O128" s="2" t="s">
         <v>39</v>
@@ -7446,49 +7560,49 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>301</v>
+        <v>151</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M129" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -7504,23 +7618,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7528,16 +7642,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7548,20 +7662,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>232.67</v>
+        <v>28.99</v>
       </c>
       <c r="J5" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K22">
         <v>85</v>
@@ -7569,7 +7683,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -7577,7 +7691,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -7608,12 +7722,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="B2">
         <v>128</v>
@@ -7627,43 +7741,43 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>232.67</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -7672,39 +7786,39 @@
         <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10">
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E11">
         <v>20</v>
@@ -7716,83 +7830,83 @@
         <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K11">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="M11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N11">
         <v>25</v>
       </c>
       <c r="P11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E12">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12">
         <v>78</v>
       </c>
       <c r="J12" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="K12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q12">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N13">
         <v>7</v>
@@ -7801,46 +7915,64 @@
         <v>28</v>
       </c>
       <c r="Q13">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="Q14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="13:14" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
       <c r="M15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
       <c r="M16" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -7856,10 +7988,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -7867,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7875,142 +8007,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F22" s="2">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F24" s="2">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>225</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F25" s="2">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>227</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F26" s="2">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>228</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>281</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>282</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>270</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="F29" s="2">
-        <v>162</v>
+        <v>285</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
